--- a/Gant Diagram.xlsx
+++ b/Gant Diagram.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/jerome_lin_epita_fr/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A75189E7-61F6-4D1E-8E38-ED81D6868BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{067E8CFB-91F5-4F96-B027-95B3F4A41387}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395F06F7-4037-4A86-B047-AF44580DB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{075CC9C5-0B01-464B-A6D3-CE19157420C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{075CC9C5-0B01-464B-A6D3-CE19157420C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Tâches</t>
   </si>
@@ -108,6 +108,21 @@
   </si>
   <si>
     <t>Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jérôme </t>
+  </si>
+  <si>
+    <t>Achref</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Everyone</t>
   </si>
 </sst>
 </file>
@@ -126,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,8 +160,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -156,14 +195,14 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </left>
       <right/>
       <top style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -171,33 +210,33 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </right>
       <top style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </left>
       <right/>
       <top style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -206,7 +245,7 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -214,11 +253,20 @@
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </right>
       <top style="medium">
-        <color rgb="FF0070C0"/>
+        <color rgb="FF99CCFF"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF99CCFF"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -226,17 +274,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -246,8 +321,8 @@
   <colors>
     <mruColors>
       <color rgb="FF66CCFF"/>
+      <color rgb="FF99CCFF"/>
       <color rgb="FF3399FF"/>
-      <color rgb="FF99CCFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -262,7 +337,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -578,14 +653,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66D2D9C-D31A-43FD-9C1D-D5C4940B7B2D}">
-  <dimension ref="A1:AB24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AF32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="28" width="5.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="28" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,7 +675,7 @@
         <v>45600</v>
       </c>
       <c r="D1" s="3">
-        <f t="shared" ref="D1:AB1" si="0">DATE(YEAR(C1), MONTH(C1), DAY(C1) + 7)</f>
+        <f t="shared" ref="D1:AC1" si="0">DATE(YEAR(C1), MONTH(C1), DAY(C1) + 7)</f>
         <v>45607</v>
       </c>
       <c r="E1" s="3">
@@ -696,357 +774,400 @@
         <f t="shared" si="0"/>
         <v>45775</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AC1" s="3">
+        <f t="shared" si="0"/>
+        <v>45782</v>
+      </c>
+      <c r="AD1" s="3">
+        <f t="shared" ref="AD1" si="1">DATE(YEAR(AC1), MONTH(AC1), DAY(AC1) + 7)</f>
+        <v>45789</v>
+      </c>
+      <c r="AE1" s="3">
+        <f t="shared" ref="AE1:AF1" si="2">DATE(YEAR(AD1), MONTH(AD1), DAY(AD1) + 7)</f>
+        <v>45796</v>
+      </c>
+      <c r="AF1" s="4"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="18"/>
+    </row>
+    <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="19"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="21"/>
+    </row>
+    <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="14"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="6"/>
-    </row>
-    <row r="7" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="19"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="21"/>
+    </row>
+    <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="11"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="6"/>
-    </row>
-    <row r="11" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T10" s="19"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="21"/>
+    </row>
+    <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="6"/>
-    </row>
-    <row r="12" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="11"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="13"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="6"/>
-    </row>
-    <row r="14" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="24"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="26"/>
+    </row>
+    <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="6"/>
-    </row>
-    <row r="15" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="16"/>
+    </row>
+    <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="6"/>
-    </row>
-    <row r="16" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="11"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="13"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="19"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="6"/>
-    </row>
-    <row r="19" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="21"/>
+    </row>
+    <row r="19" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="6"/>
-    </row>
-    <row r="20" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="11"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="13"/>
+    </row>
+    <row r="20" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N20" s="4"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="6"/>
-    </row>
-    <row r="21" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="5"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="7"/>
+    </row>
+    <row r="21" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N21" s="4"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="6"/>
-    </row>
-    <row r="22" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="5"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="7"/>
+    </row>
+    <row r="22" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="6"/>
-    </row>
-    <row r="23" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="27"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="31"/>
+    </row>
+    <row r="23" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="8"/>
-    </row>
-    <row r="24" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="24"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="26"/>
+    </row>
+    <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="6"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="28"/>
+      <c r="W24" s="28"/>
+      <c r="X24" s="28"/>
+      <c r="Y24" s="28"/>
+      <c r="Z24" s="28"/>
+      <c r="AA24" s="28"/>
+      <c r="AB24" s="29"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="32"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="33"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="34"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="35"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Gant Diagram.xlsx
+++ b/Gant Diagram.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linje\Documents\Project\An-Era-of-the-Seas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395F06F7-4037-4A86-B047-AF44580DB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177C6836-522F-4E10-A04A-E08BA7AB031A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{075CC9C5-0B01-464B-A6D3-CE19157420C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{075CC9C5-0B01-464B-A6D3-CE19157420C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -270,16 +270,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF99CCFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF99CCFF"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF99CCFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -297,7 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -310,8 +330,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -320,8 +341,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF99CCFF"/>
       <color rgb="FF66CCFF"/>
-      <color rgb="FF99CCFF"/>
       <color rgb="FF3399FF"/>
     </mruColors>
   </colors>
@@ -337,7 +358,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -657,13 +678,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AF32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="28" width="5.44140625" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="28" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -783,12 +804,12 @@
         <v>45789</v>
       </c>
       <c r="AE1" s="3">
-        <f t="shared" ref="AE1:AF1" si="2">DATE(YEAR(AD1), MONTH(AD1), DAY(AD1) + 7)</f>
+        <f t="shared" ref="AE1" si="2">DATE(YEAR(AD1), MONTH(AD1), DAY(AD1) + 7)</f>
         <v>45796</v>
       </c>
       <c r="AF1" s="4"/>
     </row>
-    <row r="2" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -801,7 +822,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="10"/>
     </row>
-    <row r="3" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -814,7 +835,7 @@
       <c r="J3" s="17"/>
       <c r="K3" s="18"/>
     </row>
-    <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -827,7 +848,7 @@
       <c r="O4" s="20"/>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -841,7 +862,7 @@
       <c r="K5" s="22"/>
       <c r="L5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -857,7 +878,7 @@
       <c r="R6" s="20"/>
       <c r="S6" s="21"/>
     </row>
-    <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -868,7 +889,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -878,7 +899,7 @@
       <c r="L8" s="15"/>
       <c r="M8" s="16"/>
     </row>
-    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -891,7 +912,7 @@
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -900,7 +921,7 @@
       <c r="V10" s="20"/>
       <c r="W10" s="21"/>
     </row>
-    <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -911,7 +932,7 @@
       <c r="Q11" s="12"/>
       <c r="R11" s="13"/>
     </row>
-    <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -925,7 +946,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -945,7 +966,7 @@
       <c r="V13" s="25"/>
       <c r="W13" s="26"/>
     </row>
-    <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -969,9 +990,16 @@
       <c r="U14" s="15"/>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
-      <c r="X14" s="16"/>
-    </row>
-    <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="15"/>
+      <c r="AE14" s="16"/>
+    </row>
+    <row r="15" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -992,9 +1020,13 @@
       <c r="X15" s="12"/>
       <c r="Y15" s="12"/>
       <c r="Z15" s="12"/>
-      <c r="AA15" s="13"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="13"/>
+    </row>
+    <row r="16" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1004,7 +1036,7 @@
       <c r="G16" s="20"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1014,7 +1046,7 @@
       <c r="G17" s="28"/>
       <c r="H17" s="29"/>
     </row>
-    <row r="18" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1028,7 +1060,7 @@
       <c r="P18" s="20"/>
       <c r="Q18" s="21"/>
     </row>
-    <row r="19" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1042,7 +1074,7 @@
       <c r="R19" s="12"/>
       <c r="S19" s="13"/>
     </row>
-    <row r="20" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1052,7 +1084,7 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="7"/>
     </row>
-    <row r="21" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1062,7 +1094,7 @@
       <c r="Q21" s="6"/>
       <c r="R21" s="7"/>
     </row>
-    <row r="22" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1086,27 +1118,33 @@
       <c r="Y22" s="30"/>
       <c r="Z22" s="30"/>
       <c r="AA22" s="30"/>
-      <c r="AB22" s="31"/>
-    </row>
-    <row r="23" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AB22" s="30"/>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="31"/>
+    </row>
+    <row r="23" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25"/>
-      <c r="AB23" s="26"/>
-    </row>
-    <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="14"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="15"/>
+      <c r="AC23" s="15"/>
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="16"/>
+    </row>
+    <row r="24" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -1122,49 +1160,52 @@
       <c r="M24" s="28"/>
       <c r="N24" s="28"/>
       <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="28"/>
-      <c r="X24" s="28"/>
-      <c r="Y24" s="28"/>
-      <c r="Z24" s="28"/>
-      <c r="AA24" s="28"/>
-      <c r="AB24" s="29"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="36"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="36"/>
+      <c r="AE24" s="37"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="32"/>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="33"/>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
       <c r="B30" s="34"/>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="35"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B31" s="22"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="36"/>
+      <c r="B32" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
